--- a/content/spreadsheets/Project-Management-Tracker.xlsx
+++ b/content/spreadsheets/Project-Management-Tracker.xlsx
@@ -2,7 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -2628,7 +2627,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="70">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="J6:L6"/>
@@ -3685,7 +3683,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <autoFilter ref="A4:L24"/>
   <mergeCells count="4">
     <mergeCell ref="A3:L3"/>
@@ -7181,7 +7178,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <autoFilter ref="A4:K84"/>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
@@ -11181,7 +11177,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="5">
     <mergeCell ref="E2:W2"/>
     <mergeCell ref="A1:W1"/>
@@ -11846,7 +11841,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <autoFilter ref="A4:F34"/>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
@@ -12714,7 +12708,6 @@
       <c r="H70" s="4" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="26">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B14:G14"/>
